--- a/data/analysis_panns/sound_class_eval_panns_w10_0s_h5_0s.xlsx
+++ b/data/analysis_panns/sound_class_eval_panns_w10_0s_h5_0s.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="25">
   <si>
     <t>class</t>
   </si>
@@ -73,9 +73,6 @@
   </si>
   <si>
     <t>skidding</t>
-  </si>
-  <si>
-    <t>speech</t>
   </si>
   <si>
     <t>tire_squeal</t>
@@ -463,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -691,38 +688,12 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-      <c r="H10">
         <v>5</v>
       </c>
     </row>
@@ -738,31 +709,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -799,7 +770,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>132</v>
@@ -835,31 +806,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -896,7 +867,7 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>189</v>
@@ -932,31 +903,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -993,7 +964,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>169</v>
@@ -1029,31 +1000,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1155,31 +1126,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1195,17 +1166,8 @@
       <c r="D2">
         <v>53</v>
       </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>240</v>
-      </c>
       <c r="H2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -1224,17 +1186,8 @@
       <c r="D3">
         <v>59</v>
       </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>240</v>
-      </c>
       <c r="H3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -1253,17 +1206,8 @@
       <c r="D4">
         <v>130</v>
       </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>240</v>
-      </c>
       <c r="H4">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -1281,31 +1225,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1407,31 +1351,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1447,17 +1391,8 @@
       <c r="D2">
         <v>36</v>
       </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>240</v>
-      </c>
       <c r="H2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -1476,17 +1411,8 @@
       <c r="D3">
         <v>40</v>
       </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>240</v>
-      </c>
       <c r="H3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -1504,31 +1430,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1544,17 +1470,8 @@
       <c r="D2">
         <v>44</v>
       </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>240</v>
-      </c>
       <c r="H2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -1573,17 +1490,8 @@
       <c r="D3">
         <v>123</v>
       </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>240</v>
-      </c>
       <c r="H3">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -1601,31 +1509,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1641,17 +1549,8 @@
       <c r="D2">
         <v>52</v>
       </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>240</v>
-      </c>
       <c r="H2">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -1670,17 +1569,8 @@
       <c r="D3">
         <v>72</v>
       </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>240</v>
-      </c>
       <c r="H3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -1698,31 +1588,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1795,31 +1685,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1863,31 +1753,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1903,17 +1793,8 @@
       <c r="D2">
         <v>138</v>
       </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>240</v>
-      </c>
       <c r="H2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -1931,31 +1812,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1971,17 +1852,8 @@
       <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>240</v>
-      </c>
       <c r="H2">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -1999,31 +1871,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9">

--- a/data/analysis_panns/sound_class_eval_panns_w10_0s_h5_0s.xlsx
+++ b/data/analysis_panns/sound_class_eval_panns_w10_0s_h5_0s.xlsx
@@ -22,13 +22,19 @@
     <sheet name="Scene_15" sheetId="13" r:id="rId13"/>
     <sheet name="Scene_16" sheetId="14" r:id="rId14"/>
     <sheet name="Scene_17" sheetId="15" r:id="rId15"/>
+    <sheet name="Scene_29" sheetId="16" r:id="rId16"/>
+    <sheet name="Scene_30" sheetId="17" r:id="rId17"/>
+    <sheet name="Scene_31" sheetId="18" r:id="rId18"/>
+    <sheet name="Scene_32" sheetId="19" r:id="rId19"/>
+    <sheet name="Scene_33" sheetId="20" r:id="rId20"/>
+    <sheet name="Scene_34" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="25">
   <si>
     <t>class</t>
   </si>
@@ -1344,6 +1350,378 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>35</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>36</v>
+      </c>
+      <c r="D3">
+        <v>37</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>50</v>
+      </c>
+      <c r="D4">
+        <v>52</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>122</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>108</v>
+      </c>
+      <c r="D2">
+        <v>138</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>240</v>
+      </c>
+      <c r="H2">
+        <v>30</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>138</v>
+      </c>
+      <c r="D3">
+        <v>240</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>240</v>
+      </c>
+      <c r="H3">
+        <v>102</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>103</v>
+      </c>
+      <c r="D2">
+        <v>138</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>240</v>
+      </c>
+      <c r="H2">
+        <v>35</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>138</v>
+      </c>
+      <c r="D3">
+        <v>182</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>240</v>
+      </c>
+      <c r="H3">
+        <v>44</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I3"/>
@@ -1413,6 +1791,200 @@
       </c>
       <c r="H3">
         <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <v>28</v>
+      </c>
+      <c r="D2">
+        <v>62</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>240</v>
+      </c>
+      <c r="H2">
+        <v>34</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>63</v>
+      </c>
+      <c r="D3">
+        <v>103</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>240</v>
+      </c>
+      <c r="H3">
+        <v>40</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>240</v>
+      </c>
+      <c r="H2">
+        <v>50</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>50</v>
+      </c>
+      <c r="D3">
+        <v>120</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>240</v>
+      </c>
+      <c r="H3">
+        <v>70</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
